--- a/models/4063_DCF_Model_20260906.xlsx
+++ b/models/4063_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBC2EF53-271D-4270-A7B6-2D29BBA9B532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F9B44C-9A46-4CC8-A53D-4D9BF4EC2C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="351">
   <si>
     <t>DISCLAIMER: This is a sample analysis for demonstration purposes only. It does not constitute investment advice.</t>
   </si>
@@ -792,7 +792,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Generated by pipeline on 2026-09-06 18:53, template rev 63983ab</t>
+    <t>Generated by pipeline on 2026-09-06 23:18, template rev 041abe3</t>
   </si>
   <si>
     <t>初期生成（手修正なし）</t>
@@ -825,6 +825,12 @@
     <t>value</t>
   </si>
   <si>
+    <t>annual_doc_ids</t>
+  </si>
+  <si>
+    <t>2026-03-31=S100YE9I, 2025-03-31=S100W0RG, 2024-03-31=S100TO0V, 2023-03-31=S100R9Y6, 2022-03-31=S100OLVL</t>
+  </si>
+  <si>
     <t>auto_log_entries</t>
   </si>
   <si>
@@ -972,6 +978,12 @@
     <t>0.093905</t>
   </si>
   <si>
+    <t>disclosure_basis_date</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
     <t>fs_year_coverage</t>
   </si>
   <si>
@@ -999,7 +1011,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-09-06 18:53:00</t>
+    <t>2026-09-06 23:18:21</t>
   </si>
   <si>
     <t>guidance_note</t>
@@ -1071,7 +1083,7 @@
     <t>template_rev</t>
   </si>
   <si>
-    <t>63983ab</t>
+    <t>041abe3</t>
   </si>
   <si>
     <t>ticker</t>
@@ -6509,7 +6521,7 @@
   <sheetPr>
     <tabColor rgb="FF808080"/>
   </sheetPr>
-  <dimension ref="B2:G60"/>
+  <dimension ref="B2:G62"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -6627,15 +6639,15 @@
         <v>269</v>
       </c>
       <c r="C17" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C18" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="14" x14ac:dyDescent="0.3">
@@ -6675,23 +6687,23 @@
         <v>280</v>
       </c>
       <c r="C23" t="s">
-        <v>4</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C24" t="s">
-        <v>250</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C25" t="s">
-        <v>283</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="14" x14ac:dyDescent="0.3">
@@ -6699,23 +6711,23 @@
         <v>284</v>
       </c>
       <c r="C26" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C27" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C28" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
     </row>
     <row r="29" spans="2:3" ht="14" x14ac:dyDescent="0.3">
@@ -6739,31 +6751,31 @@
         <v>292</v>
       </c>
       <c r="C31" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C32" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C33" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C34" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
     </row>
     <row r="35" spans="2:3" ht="14" x14ac:dyDescent="0.3">
@@ -6811,15 +6823,15 @@
         <v>307</v>
       </c>
       <c r="C40" t="s">
-        <v>275</v>
+        <v>308</v>
       </c>
     </row>
     <row r="41" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C41" t="s">
-        <v>309</v>
+        <v>277</v>
       </c>
     </row>
     <row r="42" spans="2:3" ht="14" x14ac:dyDescent="0.3">
@@ -6971,6 +6983,22 @@
         <v>346</v>
       </c>
       <c r="C60" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B61" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C61" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B62" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C62" t="s">
         <v>211</v>
       </c>
     </row>

--- a/models/4063_DCF_Model_20260906.xlsx
+++ b/models/4063_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F9B44C-9A46-4CC8-A53D-4D9BF4EC2C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4991CF5-4345-40B3-9F15-AE71ADDBA497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -614,7 +614,7 @@
     <t>Comparable Company Analysis</t>
   </si>
   <si>
-    <t>Peer prices as of 2026-09-06 (Mkt Cap / EV of peer rows are static CSV values; the subject row is live-linked to Executive Summary)</t>
+    <t>Peer prices as of 2026-09-07 (Mkt Cap / EV of peer rows are static CSV values; the subject row is live-linked to Executive Summary)</t>
   </si>
   <si>
     <t>Mkt Cap
@@ -786,13 +786,13 @@
     <t>状態</t>
   </si>
   <si>
-    <t>2026-09-06</t>
+    <t>2026-09-07</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>Generated by pipeline on 2026-09-06 23:18, template rev 041abe3</t>
+    <t>Generated by pipeline on 2026-09-07 02:28, template rev 15b64f7</t>
   </si>
   <si>
     <t>初期生成（手修正なし）</t>
@@ -1011,7 +1011,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-09-06 23:18:21</t>
+    <t>2026-09-07 02:28:50</t>
   </si>
   <si>
     <t>guidance_note</t>
@@ -1083,7 +1083,7 @@
     <t>template_rev</t>
   </si>
   <si>
-    <t>041abe3</t>
+    <t>15b64f7</t>
   </si>
   <si>
     <t>ticker</t>
